--- a/Model Evaluation & Testing/experiment_log.xlsx
+++ b/Model Evaluation & Testing/experiment_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W4"/>
+  <dimension ref="A1:Z23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -532,6 +532,21 @@
           <t>caught_by_zscore_only</t>
         </is>
       </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>training_rows</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>total_refits</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -609,6 +624,9 @@
       <c r="W2" t="n">
         <v>63</v>
       </c>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -686,6 +704,9 @@
       <c r="W3" t="n">
         <v>14</v>
       </c>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -762,6 +783,1681 @@
       </c>
       <c r="W4" t="n">
         <v>0</v>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-09-05T12:26:37</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ART3</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>30</v>
+      </c>
+      <c r="G5" t="n">
+        <v>200</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>{"spike": 20, "frozen": 20, "drift": 20, "dropout": 20}</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>880</v>
+      </c>
+      <c r="K5" t="n">
+        <v>787</v>
+      </c>
+      <c r="L5" t="n">
+        <v>597</v>
+      </c>
+      <c r="M5" t="n">
+        <v>67.84090909090909</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.758576874205845</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.678409090909091</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.7162567486502699</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>b'\x8a\x07\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>b'\xbe\x00\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>b'\x1b\x01\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>b'U\x02\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="n">
+        <v>0.8423333333333334</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>6240</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-09-05T12:33:56</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ART3</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>30</v>
+      </c>
+      <c r="G6" t="n">
+        <v>200</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>{"spike": 20, "frozen": 10, "drift": 10, "dropout": 10}</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>450</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1809</v>
+      </c>
+      <c r="L6" t="n">
+        <v>371</v>
+      </c>
+      <c r="M6" t="n">
+        <v>82.44444444444444</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.205085682697623</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.8244444444444444</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.3284639220894201</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>b'X\x04\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>b'\x9e\x05\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>b'O\x00\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>b's\x01\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="n">
+        <v>0.4943333333333333</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>4550</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-09-05T12:35:31</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ART3</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>30</v>
+      </c>
+      <c r="G7" t="n">
+        <v>200</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>{"spike": 1, "frozen": 1, "drift": 1, "dropout": 1}</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>44</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1548</v>
+      </c>
+      <c r="L7" t="n">
+        <v>41</v>
+      </c>
+      <c r="M7" t="n">
+        <v>93.18181818181817</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.02648578811369509</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.9318181818181818</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.05150753768844221</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>b'\xa9\x05\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>b'\xe3\x05\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>b'\x03\x00\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>b')\x00\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="n">
+        <v>0.4966666666666666</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>7506</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-09-05T12:36:10</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ART3</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>30</v>
+      </c>
+      <c r="G8" t="n">
+        <v>200</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>{"spike": 5, "frozen": 5, "drift": 5, "dropout": 5}</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>220</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1729</v>
+      </c>
+      <c r="L8" t="n">
+        <v>201</v>
+      </c>
+      <c r="M8" t="n">
+        <v>91.36363636363637</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.1162521688837478</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.9136363636363637</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.2062596203181118</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>b'\xe4\x04\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>b'\xf8\x05\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>b'\x13\x00\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>b'\xc9\x00\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="n">
+        <v>0.4843333333333333</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>10286</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-09-05T12:36:43</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ART3</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="n">
+        <v>30</v>
+      </c>
+      <c r="G9" t="n">
+        <v>200</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>{"spike": 15, "frozen": 15, "drift": 15, "dropout": 15}</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>660</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1750</v>
+      </c>
+      <c r="L9" t="n">
+        <v>543</v>
+      </c>
+      <c r="M9" t="n">
+        <v>82.27272727272728</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.3102857142857143</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.8227272727272728</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.4506224066390042</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>b'm\x04\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>b'\xb7\x04\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>b'u\x00\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>b'\x1f\x02\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="n">
+        <v>0.5586666666666666</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>12626</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-09-05T12:37:33</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ART3</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="n">
+        <v>30</v>
+      </c>
+      <c r="G10" t="n">
+        <v>200</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>{"spike": 25, "frozen": 10, "drift": 1, "dropout": 25}</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>200</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1644</v>
+      </c>
+      <c r="L10" t="n">
+        <v>182</v>
+      </c>
+      <c r="M10" t="n">
+        <v>91</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.110705596107056</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.1973969631236442</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>b':\x05\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>b'\xb6\x05\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>b'\x12\x00\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>b'\xb6\x00\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="n">
+        <v>0.5066666666666667</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>15426</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-09-05T12:38:02</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ART3</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="n">
+        <v>30</v>
+      </c>
+      <c r="G11" t="n">
+        <v>200</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>{"spike": 25, "frozen": 25, "drift": 25, "dropout": 25}</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>1100</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1479</v>
+      </c>
+      <c r="L11" t="n">
+        <v>876</v>
+      </c>
+      <c r="M11" t="n">
+        <v>79.63636363636364</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.5922920892494929</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.7963636363636364</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.6793330748352074</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>b'\x11\x05\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>b'[\x02\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>b'\xe0\x00\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>b'l\x03\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="n">
+        <v>0.7243333333333334</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>17326</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-09-05T12:38:34</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ART3</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" t="n">
+        <v>30</v>
+      </c>
+      <c r="G12" t="n">
+        <v>200</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>{"spike": 30}</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>30</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1208</v>
+      </c>
+      <c r="L12" t="n">
+        <v>30</v>
+      </c>
+      <c r="M12" t="n">
+        <v>100</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.02483443708609271</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.04846526655896607</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>b'\x00\x07\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>b'\x9a\x04\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>b'\x00\x00\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>b'\x1e\x00\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="n">
+        <v>0.6073333333333333</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>20296</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-09-05T12:39:00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ART3</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>30</v>
+      </c>
+      <c r="G13" t="n">
+        <v>200</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>{"spike": 50}</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>50</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1803</v>
+      </c>
+      <c r="L13" t="n">
+        <v>50</v>
+      </c>
+      <c r="M13" t="n">
+        <v>100</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.02773155851358846</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.05396654074473826</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>b'\xad\x04\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>b'\xd9\x06\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>b'\x00\x00\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>b'2\x00\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="n">
+        <v>0.4156666666666667</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>23246</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-09-05T12:39:49</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ART3</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>30</v>
+      </c>
+      <c r="G14" t="n">
+        <v>200</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>{"spike": 10}</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>10</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1680</v>
+      </c>
+      <c r="L14" t="n">
+        <v>10</v>
+      </c>
+      <c r="M14" t="n">
+        <v>100</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.005952380952380952</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.01183431952662722</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>b'(\x05\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>b'\x86\x06\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>b'\x00\x00\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>b'\n\x00\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="n">
+        <v>0.4433333333333334</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>26236</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-09-05T12:40:21</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ART3</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" t="n">
+        <v>30</v>
+      </c>
+      <c r="G15" t="n">
+        <v>200</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>{"frozen": 20}</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>240</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1860</v>
+      </c>
+      <c r="L15" t="n">
+        <v>212</v>
+      </c>
+      <c r="M15" t="n">
+        <v>88.33333333333333</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.1139784946236559</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.8833333333333333</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.2019047619047619</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>b'X\x04\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>b'p\x06\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>b'\x1c\x00\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>b'\xd4\x00\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="n">
+        <v>0.4413333333333334</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>28996</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-09-05T12:40:55</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ART3</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" t="n">
+        <v>30</v>
+      </c>
+      <c r="G16" t="n">
+        <v>200</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>{"frozen": 20}</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>240</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1505</v>
+      </c>
+      <c r="L16" t="n">
+        <v>159</v>
+      </c>
+      <c r="M16" t="n">
+        <v>66.25</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.1056478405315615</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.6625</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.1822349570200573</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>b'\x86\x05\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>b'B\x05\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>b'Q\x00\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>b'\x9f\x00\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="n">
+        <v>0.5243333333333333</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>31756</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-09-05T12:41:24</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ART3</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" t="n">
+        <v>30</v>
+      </c>
+      <c r="G17" t="n">
+        <v>200</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>{"frozen": 5}</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>60</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1673</v>
+      </c>
+      <c r="L17" t="n">
+        <v>55</v>
+      </c>
+      <c r="M17" t="n">
+        <v>91.66666666666666</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.0328750747160789</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.06347374495095211</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>b'*\x05\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>b'R\x06\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>b'\x05\x00\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>b'7\x00\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="n">
+        <v>0.459</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>34696</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-09-05T12:42:09</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ART3</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="n">
+        <v>30</v>
+      </c>
+      <c r="G18" t="n">
+        <v>200</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>{"drift": 20}</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>600</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1564</v>
+      </c>
+      <c r="L18" t="n">
+        <v>508</v>
+      </c>
+      <c r="M18" t="n">
+        <v>84.66666666666667</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.3248081841432225</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.8466666666666667</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.4695009242144177</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>b'@\x05\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>b' \x04\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>b'\\\x00\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>b'\xfc\x01\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="n">
+        <v>0.6173333333333333</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>37096</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-09-05T12:47:22</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ART3</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" t="n">
+        <v>30</v>
+      </c>
+      <c r="G19" t="n">
+        <v>200</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>{"drift": 20}</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>600</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1607</v>
+      </c>
+      <c r="L19" t="n">
+        <v>536</v>
+      </c>
+      <c r="M19" t="n">
+        <v>89.33333333333333</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.3335407591785937</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.8933333333333333</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.4857272315360218</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>b'1\x05\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>b'/\x04\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>b'@\x00\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>b'\x18\x02\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="n">
+        <v>0.6216666666666667</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>39496</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-09-05T12:47:59</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ART3</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" t="n">
+        <v>30</v>
+      </c>
+      <c r="G20" t="n">
+        <v>200</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>{"drift": 8}</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>240</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1453</v>
+      </c>
+      <c r="L20" t="n">
+        <v>186</v>
+      </c>
+      <c r="M20" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.1280110116999312</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.2197282929710573</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>b'\xd5\x05\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>b'\xf3\x04\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>b'6\x00\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>b'\xba\x00\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="n">
+        <v>0.5596666666666666</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>42256</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-09-05T12:48:38</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ART3</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" t="n">
+        <v>30</v>
+      </c>
+      <c r="G21" t="n">
+        <v>200</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>{"drift": 3}</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>90</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1821</v>
+      </c>
+      <c r="L21" t="n">
+        <v>85</v>
+      </c>
+      <c r="M21" t="n">
+        <v>94.44444444444444</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.04667764964305327</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.08895866038723181</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>b'\x96\x04\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>b'\xc8\x06\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>b'\x05\x00\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>b'U\x00\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="n">
+        <v>0.4196666666666667</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>45166</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-09-05T12:49:17</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ART3</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" t="n">
+        <v>30</v>
+      </c>
+      <c r="G22" t="n">
+        <v>200</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>{"dropout": 40}</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>40</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1781</v>
+      </c>
+      <c r="L22" t="n">
+        <v>40</v>
+      </c>
+      <c r="M22" t="n">
+        <v>100</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.02245929253228523</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.04393190554640308</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>b'\xc3\x04\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>b'\xcd\x06\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>b'\x00\x00\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>b'(\x00\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="n">
+        <v>0.4196666666666667</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>48126</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-09-05T12:51:17</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ART3</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" t="n">
+        <v>30</v>
+      </c>
+      <c r="G23" t="n">
+        <v>200</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>{"spike": 20, "frozen": 20, "drift": 20, "dropout": 20}</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>880</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1715</v>
+      </c>
+      <c r="L23" t="n">
+        <v>736</v>
+      </c>
+      <c r="M23" t="n">
+        <v>83.63636363636363</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.4291545189504373</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.8363636363636363</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.5672447013487476</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>b'u\x04\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>b'\xd3\x03\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>b'\x90\x00\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>b'\xe0\x02\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="n">
+        <v>0.6256666666666667</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>50246</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>242</v>
       </c>
     </row>
   </sheetData>

--- a/Model Evaluation & Testing/experiment_log.xlsx
+++ b/Model Evaluation & Testing/experiment_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z23"/>
+  <dimension ref="A1:Z26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2460,6 +2460,270 @@
         <v>242</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-09-05T15:19:37</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ART3</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" t="n">
+        <v>30</v>
+      </c>
+      <c r="G24" t="n">
+        <v>200</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>{"spike": 20, "frozen": 20, "drift": 20, "dropout": 20}</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>880</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1803</v>
+      </c>
+      <c r="L24" t="n">
+        <v>763</v>
+      </c>
+      <c r="M24" t="n">
+        <v>86.70454545454545</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.42318358291736</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.8670454545454546</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.5687663063734626</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>b'8\x04\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>b'\x10\x04\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>b'u\x00\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>b'\xfb\x02\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="n">
+        <v>0.6143333333333333</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>4120</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-09-05T15:51:23</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ART3</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" t="n">
+        <v>30</v>
+      </c>
+      <c r="G25" t="n">
+        <v>200</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>{"spike": 20, "frozen": 20, "drift": 20, "dropout": 20}</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>880</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1730</v>
+      </c>
+      <c r="L25" t="n">
+        <v>728</v>
+      </c>
+      <c r="M25" t="n">
+        <v>82.72727272727273</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.4208092485549133</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.8272727272727273</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.5578544061302682</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>b'^\x04\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>b'\xea\x03\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>b'\x98\x00\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>b'\xd8\x02\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="n">
+        <v>0.6153333333333333</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>4120</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-09-05T17:33:13</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ART3</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" t="n">
+        <v>30</v>
+      </c>
+      <c r="G26" t="n">
+        <v>200</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>{"spike": 20, "frozen": 20, "drift": 20, "dropout": 20}</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>880</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1989</v>
+      </c>
+      <c r="L26" t="n">
+        <v>743</v>
+      </c>
+      <c r="M26" t="n">
+        <v>84.43181818181819</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.3735545500251383</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.8443181818181819</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.5179505054025793</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>b'j\x03\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>b'\xde\x04\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>b'\x89\x00\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>b'\xe7\x02\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="n">
+        <v>0.539</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>4120</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
